--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -44685,7 +44685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E380"/>
+  <dimension ref="A1:E375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -52000,7 +52000,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -52025,7 +52025,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -52050,7 +52050,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -52075,7 +52075,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -52100,7 +52100,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -52125,17 +52125,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -52144,23 +52144,23 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -52169,23 +52169,23 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -52194,28 +52194,28 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -52225,22 +52225,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -52250,7 +52250,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -52260,22 +52260,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -52285,7 +52285,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -52294,13 +52294,13 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -52310,7 +52310,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -52319,13 +52319,13 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -52335,22 +52335,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -52360,12 +52360,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -52375,7 +52375,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -52385,12 +52385,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -52400,7 +52400,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -52419,13 +52419,13 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -52435,7 +52435,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -52444,13 +52444,13 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -52460,7 +52460,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -52485,7 +52485,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -52500,17 +52500,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>SERGIPE GUIAS</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -52525,17 +52525,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SERGIPE GUIAS</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -52550,22 +52550,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>SERGIPE GUIAS</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -52575,22 +52575,22 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>SERGIPE GUIAS</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -52600,12 +52600,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>SERGIPE GUIAS</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -52619,13 +52619,13 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -52635,7 +52635,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -52644,7 +52644,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="319">
@@ -52655,12 +52655,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>SERGIPE CURSO</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -52675,22 +52675,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>SERGIPE CURSO</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -52700,22 +52700,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>SERGIPE CURSO</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -52725,57 +52725,57 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>SERGIPE CURSO</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>SERGIPE CURSO</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -52785,12 +52785,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -52800,7 +52800,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -52810,7 +52810,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -52819,13 +52819,13 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -52835,7 +52835,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -52844,13 +52844,13 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -52860,32 +52860,32 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>SERGIPE ASSESSORIA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -52900,17 +52900,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>SERGIPE ASSESSORIA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -52925,76 +52925,76 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>SERGIPE ASSESSORIA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>SERGIPE ASSESSORIA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>SERGIPE ASSESSORIA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="333">
@@ -53010,7 +53010,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -53035,7 +53035,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -53060,7 +53060,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -53075,17 +53075,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>COMUNICAÇÃO</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -53100,17 +53100,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>COMUNICAÇÃO</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -53125,17 +53125,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>COMUNICAÇÃO</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -53150,17 +53150,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>COMUNICAÇÃO</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -53175,17 +53175,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>COMUNICAÇÃO</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -53210,7 +53210,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -53235,7 +53235,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -53260,7 +53260,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -53275,22 +53275,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>BENS PÚBLICOS</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -53300,22 +53300,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>BENS PÚBLICOS</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -53325,22 +53325,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>BENS PÚBLICOS</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -53350,22 +53350,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>BENS PÚBLICOS</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -53375,22 +53375,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>BENS PÚBLICOS</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -53410,7 +53410,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -53435,7 +53435,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -53460,7 +53460,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -53475,7 +53475,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -53485,7 +53485,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -53500,7 +53500,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -53510,7 +53510,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -53525,7 +53525,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -53535,7 +53535,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -53550,7 +53550,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -53560,7 +53560,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -53575,7 +53575,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -53585,7 +53585,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -53610,7 +53610,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -53635,7 +53635,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -53660,7 +53660,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -53675,7 +53675,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -53685,7 +53685,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -53694,13 +53694,13 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -53710,7 +53710,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -53719,13 +53719,13 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -53735,7 +53735,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -53744,13 +53744,13 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -53760,7 +53760,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -53769,13 +53769,13 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -53785,7 +53785,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -53794,7 +53794,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="365">
@@ -53810,7 +53810,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -53835,7 +53835,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -53860,7 +53860,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Julho</t>
+          <t>Dezembro</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -53875,17 +53875,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>FUNDRAISING</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -53894,23 +53894,23 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>FUNDRAISING</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -53919,73 +53919,73 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>FUNDRAISING</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>FUNDRAISING</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>FUNDRAISING</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Dezembro</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -53994,13 +53994,13 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -54010,7 +54010,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -54030,12 +54030,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>GLOCAL</t>
+          <t>PROCESSO SELETIVO</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -54050,12 +54050,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>GLOCAL</t>
+          <t>PROCESSO SELETIVO</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -54065,135 +54065,10 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>Junho</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>Líder</t>
-        </is>
-      </c>
-      <c r="E376" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>Maio</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
-      <c r="E377" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Junho</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
-      <c r="E378" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>PROCESSO SELETIVO</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Maio</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
-      <c r="E379" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>PROCESSO SELETIVO</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Maio</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
-      <c r="E380" t="n">
         <v>40</v>
       </c>
     </row>
@@ -54434,7 +54309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54697,7 +54572,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -54706,7 +54581,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -54720,7 +54595,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -54729,7 +54604,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -54743,16 +54618,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -54766,7 +54641,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -54789,7 +54664,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -54812,19 +54687,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FUNDRAISING</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -54835,7 +54710,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -54858,7 +54733,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -54881,30 +54756,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GLOCAL</t>
+          <t>Instituto Unibanco | AT Seduc ES</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -54927,7 +54802,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -54939,7 +54814,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -54950,7 +54825,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -54959,7 +54834,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
@@ -54973,7 +54848,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -54982,7 +54857,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -54996,7 +54871,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -55008,7 +54883,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -55019,7 +54894,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -55042,7 +54917,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -55054,7 +54929,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -55065,19 +54940,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Instituto Unibanco | AT Seduc ES</t>
+          <t>Instituto Unibanco | Av. Executiva</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -55088,7 +54963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -55111,19 +54986,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Instituto Unibanco | Av. Executiva</t>
+          <t>Instituto Unibanco | Coordenação</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -55134,19 +55009,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Instituto Unibanco | Coordenação</t>
+          <t>Instituto Unibanco | Novo PAR</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -55157,7 +55032,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -55180,30 +55055,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Instituto Unibanco | Novo PAR</t>
+          <t>PRIME - AV IMPACTO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>master</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -55226,7 +55101,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -55249,7 +55124,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -55272,12 +55147,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>PRIME - FUNDAMENTOS</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -55295,7 +55170,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -55318,7 +55193,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -55341,7 +55216,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -55364,7 +55239,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -55387,7 +55262,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -55410,7 +55285,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -55433,12 +55308,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>PRIME - HANDS ON</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -55456,7 +55331,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -55479,7 +55354,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -55502,7 +55377,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -55525,12 +55400,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -55548,7 +55423,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -55571,7 +55446,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -55594,19 +55469,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>PROCESSO SELETIVO</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -55617,7 +55492,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -55640,19 +55515,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PROCESSO SELETIVO</t>
+          <t>REDECA</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -55663,7 +55538,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -55686,7 +55561,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -55709,7 +55584,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -55732,30 +55607,30 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>Rede Subnacional</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>csv</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -55764,7 +55639,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
         <v>12</v>
@@ -55778,7 +55653,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -55787,10 +55662,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -55801,7 +55676,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -55813,7 +55688,7 @@
         <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -55824,30 +55699,30 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rede Subnacional</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
         <v>12</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>master</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -55870,7 +55745,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -55893,19 +55768,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SERGIPE ASSESSORIA</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -55916,7 +55791,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -55939,7 +55814,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -55962,19 +55837,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SERGIPE CURSO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="n">
         <v>8</v>
-      </c>
-      <c r="D67" t="n">
-        <v>9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -55985,7 +55860,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -56008,7 +55883,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -56031,7 +55906,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -56054,7 +55929,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -56077,30 +55952,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SERGIPE GUIAS</t>
+          <t>TCE | AT (Serra, Montanha, Anchieta)</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>csv</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -56109,7 +55984,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D73" t="n">
         <v>12</v>
@@ -56123,7 +55998,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -56132,10 +56007,10 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" t="n">
         <v>7</v>
-      </c>
-      <c r="D74" t="n">
-        <v>12</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -56146,19 +56021,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TCE | AT (Serra, Montanha, Anchieta)</t>
+          <t>TCE | Coordenação</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -56174,14 +56049,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TCE | Coordenação</t>
+          <t>TCE | Curso Mun III</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D76" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -56192,7 +56067,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -56215,7 +56090,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -56238,12 +56113,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TCE | Curso Mun III</t>
+          <t>TCE | Formação (Serra, Montanha, Anchieta) - 1</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -56261,7 +56136,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -56284,19 +56159,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TCE | Formação (Serra, Montanha, Anchieta) - 1</t>
+          <t>TCE | Formação (Serra, Montanha, Anchieta) - 2 e 3</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -56307,7 +56182,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -56322,29 +56197,6 @@
         <v>11</v>
       </c>
       <c r="E82" t="inlineStr">
-        <is>
-          <t>csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Hisrael</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>TCE | Formação (Serra, Montanha, Anchieta) - 2 e 3</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>11</v>
-      </c>
-      <c r="D83" t="n">
-        <v>11</v>
-      </c>
-      <c r="E83" t="inlineStr">
         <is>
           <t>csv</t>
         </is>

--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -23,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -55,10 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,7 +443,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -533,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N425"/>
+  <dimension ref="A1:O426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,6 +631,11 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>fonte</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>presencial</t>
         </is>
       </c>
     </row>
@@ -13567,6 +13572,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -13616,6 +13626,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -13665,6 +13680,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -13715,6 +13735,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -13764,6 +13789,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -13813,6 +13843,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -13862,6 +13897,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -13911,6 +13951,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -13960,6 +14005,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -14009,6 +14059,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -14058,6 +14113,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -14107,6 +14167,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -14156,6 +14221,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -14205,6 +14275,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -14254,6 +14329,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -14303,6 +14383,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -14352,6 +14437,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -14401,6 +14491,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -14450,6 +14545,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -14499,6 +14599,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -14548,6 +14653,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -14597,6 +14707,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -14646,6 +14761,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -14695,6 +14815,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -14744,6 +14869,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -14793,6 +14923,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -14842,6 +14977,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -14891,6 +15031,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -14940,6 +15085,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -14989,6 +15139,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -15038,6 +15193,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -15087,6 +15247,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -15182,6 +15347,11 @@
           <t>EVALAC 2026</t>
         </is>
       </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -21069,6 +21239,71 @@
       <c r="N425" t="inlineStr">
         <is>
           <t>Guias</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>EVALAC 2026 — Evento presencial (7 a 11 de setembro)</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Evento de formação. Todas as reuniões e atividades anteriores são online.</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Caio; Michel</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Caio; Michel</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>2</v>
+      </c>
+      <c r="I426" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Evento de 7 a 11 de setembro</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L426" t="b">
+        <v>1</v>
+      </c>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>evento_evalac</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Presencial</t>
         </is>
       </c>
     </row>

--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -443,6 +443,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -534,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -544,7 +546,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bia B, Bia S, Caio, Carol, Cecilia, Fabrícia, Fred, Hisrael, Julia, Junior, Lorena, Luan, Luiggi, Lycia, Michel, Samu</t>
+          <t>Bia B, Bia S, Caio, Carol, Cecilia, Fabrícia, Fred, Hisrael, Julia, Junior, Lorena, Luan, Luigi, Lycia, Michel, Samu</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1167,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1219,12 +1221,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1273,12 +1275,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1327,12 +1329,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1381,12 +1383,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1439,12 +1441,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1547,12 +1549,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1703,12 +1705,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1761,12 +1763,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1815,12 +1817,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1869,12 +1871,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1923,12 +1925,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2413,12 +2415,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2467,12 +2469,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2518,12 +2520,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3043,12 +3045,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3097,12 +3099,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Caio + Luiggi</t>
+          <t>Caio + Luigi</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -21116,12 +21118,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Caio e Luiggi</t>
+          <t>Caio e Luigi</t>
         </is>
       </c>
       <c r="H423" t="n">
@@ -21165,12 +21167,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Caio e Luiggi</t>
+          <t>Caio e Luigi</t>
         </is>
       </c>
       <c r="H424" t="n">
@@ -21214,12 +21216,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Caio; Luiggi</t>
+          <t>Caio; Luigi</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Caio e Luiggi</t>
+          <t>Caio e Luigi</t>
         </is>
       </c>
       <c r="H425" t="n">
@@ -21295,7 +21297,6 @@
       <c r="L426" t="b">
         <v>1</v>
       </c>
-      <c r="M426" t="inlineStr"/>
       <c r="N426" t="inlineStr">
         <is>
           <t>evento_evalac</t>
@@ -21905,7 +21906,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -21931,7 +21932,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -21957,7 +21958,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -22009,7 +22010,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -22035,7 +22036,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -22061,7 +22062,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -22113,7 +22114,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -22211,7 +22212,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -22263,7 +22264,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -22315,7 +22316,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -22367,7 +22368,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -22419,7 +22420,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -22676,7 +22677,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -22725,7 +22726,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -22774,7 +22775,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -23045,7 +23046,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -23097,7 +23098,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -36799,7 +36800,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -36851,7 +36852,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -36903,7 +36904,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -37188,7 +37189,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -37548,7 +37549,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -37908,7 +37909,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -38268,7 +38269,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -38628,7 +38629,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -38988,7 +38989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -39348,7 +39349,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -39708,7 +39709,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -39871,7 +39872,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>projeto_alocacao</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -39912,7 +39913,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>projeto_alocacao</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -41856,7 +41857,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Luiggi</t>
+          <t>Luigi</t>
         </is>
       </c>
     </row>

--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alocacao_Gantt" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pessoas" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projetos" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carga_Esperada" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +444,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -535,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -547,6 +546,18 @@
       <c r="A14" t="inlineStr">
         <is>
           <t>Bia B, Bia S, Caio, Carol, Cecilia, Fabrícia, Fred, Hisrael, Julia, Junior, Lorena, Luan, Luigi, Lycia, Michel, Samu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carga_Esperada</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Carga esperada B/M/A por pessoa × projeto × mês (líderes preenchem nos cronogramas)</t>
         </is>
       </c>
     </row>
@@ -41976,4 +41987,7740 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D386"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>pessoa</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>projeto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>10</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>11</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PRIME - FUNDAMENTOS</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>9</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>10</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>11</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>12</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>10</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>11</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>12</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>5</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>6</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>8</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>9</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>11</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PRIME - HANDS ON</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>12</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>7</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>8</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>9</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>10</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>7</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>9</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>10</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>12</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>6</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>9</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>10</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>11</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>6</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>7</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>8</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>9</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>10</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>11</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PRIME - AV IMPACTO</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>6</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>7</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>8</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>9</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>10</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>11</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>12</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>5</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>6</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>7</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>8</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>9</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>10</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>11</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>12</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>5</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>6</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>7</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>8</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>9</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>10</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>11</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PRIME - OFICINAS INOVAÇÃO</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>12</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>5</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>6</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>7</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>8</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>9</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>6</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>7</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>8</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EVALAC</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>9</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>5</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>6</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>7</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>8</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>9</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>10</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>5</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>6</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>7</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>8</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>9</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>10</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>5</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>6</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>7</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>8</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>9</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>10</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>5</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>6</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>7</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>8</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>9</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>REDECA</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>10</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>5</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>6</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>7</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>8</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>9</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>5</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>5</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>6</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>7</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>8</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>9</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>5</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>6</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>7</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>8</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>TCE - CURSO</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>9</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>6</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>7</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>8</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>9</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>5</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>6</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>7</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>8</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>9</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>10</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>11</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>12</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>5</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>6</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>5</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>6</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>7</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>8</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>9</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>10</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>11</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>12</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>6</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>7</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>8</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>9</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TCE - ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>10</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>5</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>6</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>5</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>6</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>5</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>6</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>5</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>IU - OFICINA</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>6</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>6</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>7</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>8</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>9</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>10</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>11</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>12</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>6</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>7</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>8</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>9</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>10</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>11</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>12</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>6</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>7</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>8</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>9</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>10</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>11</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>12</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>6</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>7</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>8</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>9</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>10</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>11</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>IU - AV EXECUTIVA</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>IU - ARTIGO SISTEMA</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>5</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>IU - ARTIGO SISTEMA</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>6</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>IU - ARTIGO SISTEMA</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>5</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>IU - ARTIGO SISTEMA</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>6</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>IU - ARTIGO SISTEMA</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>5</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>IU - ARTIGO SISTEMA</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>6</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>8</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>9</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>10</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>8</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>9</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>10</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>8</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>9</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>10</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Hisrael</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>8</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Hisrael</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>9</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Hisrael</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>IU - ASSESSORIA TÉCNICA</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>10</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>5</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>6</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>5</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>6</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>5</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>6</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>5</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>6</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>5</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>6</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>8</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>9</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>10</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>11</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>12</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>11</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>12</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>8</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>9</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>10</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>11</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>12</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>8</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>9</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>10</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>11</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>12</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>8</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>9</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>10</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>11</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Fred</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>FINEP</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>12</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>6</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>7</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>8</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>6</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>7</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>8</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>6</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>7</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>8</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>6</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>7</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>8</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Hisrael</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>6</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Hisrael</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>7</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Hisrael</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>SERGIPE GUIAS</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>8</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>SERGIPE CURSO</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>8</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>SERGIPE CURSO</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>9</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SERGIPE CURSO</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>8</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>SERGIPE CURSO</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>9</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>SERGIPE CURSO</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>8</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>SERGIPE CURSO</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>9</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>10</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>11</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>12</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>10</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>11</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>12</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>10</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>11</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>SERGIPE ASSESSORIA</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>12</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>5</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>6</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>7</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>8</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>9</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>10</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>11</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>12</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>5</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>6</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>7</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>8</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>9</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>10</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>11</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>BENS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>12</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>5</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>6</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>7</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>8</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>9</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>10</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>11</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Bia B</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>12</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>5</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>6</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>7</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>8</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>9</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>10</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>11</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>12</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>5</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>6</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>7</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>8</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>9</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>10</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>11</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>FUNDRAISING</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>12</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>GLOCAL</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>5</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>GLOCAL</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>6</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>GLOCAL</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>5</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>GLOCAL</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>6</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>GLOCAL</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>5</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>GLOCAL</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>6</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>PROCESSO SELETIVO</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>5</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>PROCESSO SELETIVO</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>5</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O544"/>
+  <dimension ref="A1:O594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29064,6 +29064,2455 @@
       <c r="O544" t="inlineStr">
         <is>
           <t>Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>639</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Elaboração de Outline</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Planejamento</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Cecilia; Bia S</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Cecília e BiaS</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>2</v>
+      </c>
+      <c r="I545" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="L545" t="b">
+        <v>0</v>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>640</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Outline aprovado</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Planejamento</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Cecilia; Michel</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Cecília e Michel</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>2</v>
+      </c>
+      <c r="I546" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="L546" t="b">
+        <v>0</v>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>641</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Rascunho das Seção 0 a 2 – Ciclo da poítica pública e Teoria da Mudança</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Elaboração do texto</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Cecilia; Bia S</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Cecília e BiaS</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>2</v>
+      </c>
+      <c r="I547" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="L547" t="b">
+        <v>0</v>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>642</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Revisão do rascunho das Seção 0 a 2 – Ciclo da poítica pública e Teoria da Mudança</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Elaboração do texto</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>1</v>
+      </c>
+      <c r="I548" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="L548" t="b">
+        <v>0</v>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>643</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Rascunho da Seção 3 – Como construir a TdM,  situações problema e exemplos aplicados</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Elaboração do texto</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Cecilia; Bia S</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Cecília e BiaS</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>2</v>
+      </c>
+      <c r="I549" s="3" t="n">
+        <v>46199</v>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="L549" t="b">
+        <v>0</v>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>644</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Revisão do rascunho da Seção 3 – Como construir a TdM,  situações problema e exemplos aplicados</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Elaboração do texto</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>1</v>
+      </c>
+      <c r="I550" s="3" t="n">
+        <v>46199</v>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L550" t="b">
+        <v>0</v>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>645</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Revisão, ajustes e entrega da primeira versão completa do mini-guia</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Elaboração do texto</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Cecilia; Bia S</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Cecília e BiaS</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>2</v>
+      </c>
+      <c r="I551" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L551" t="b">
+        <v>1</v>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>646</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>MiniGuia</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Revisão Final</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Elaboração do texto</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>1</v>
+      </c>
+      <c r="I552" s="3" t="n">
+        <v>46206</v>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L552" t="b">
+        <v>0</v>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>MiniGuia 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>647</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Concept note</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Concept note finalizado com Versão executiva</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>4</v>
+      </c>
+      <c r="I553" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="L553" t="b">
+        <v>0</v>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>648</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Escutas com parceiros de rede</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Mapear instituições com experiência em redes (BID, RBMA e outras); elaborar roteiro de escuta (governança, sustentabilidade, engajamento, desenho operacional); conduzir as escutas.</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>3</v>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="L554" t="b">
+        <v>0</v>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>649</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Sistematização dos aprendizados das escutas</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Consolidar em documento os aprendizados das escutas, para alimentar o desenho da rede e a Teoria da Mudança.</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>3</v>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L555" t="b">
+        <v>0</v>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>650</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Elaboração da Teoria da Mudança</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>redigir versão preliminar (a validar na Fase 3).</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>3</v>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L556" t="b">
+        <v>0</v>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>651</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Apresentação do concept note ao BID</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Lycia enviará por e-mail</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Lycia</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Lycia</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>1</v>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="L557" t="b">
+        <v>0</v>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>652</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Definição do plano de comunicação e criação da identidade visual piloto</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>desenvolver identidade visual piloto (logo, paleta, aplicação); validar internamente.</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>4</v>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L558" t="b">
+        <v>0</v>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>653</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Mapeamento dos destinatários da carta de intenção</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Identificar entes prioritários e os titulares dos órgãos de centro de governo; organizar base de contatos para abordagem a partir de 2027.</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>3</v>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L559" t="b">
+        <v>0</v>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>654</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Rodada de escuta com entes de referência</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Agendar e conduzir escutas individuais com entes de referência para co-construção e endosso inicial; registrar contribuições e ajustar a proposta.</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>3</v>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="L560" t="b">
+        <v>0</v>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>655</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Fase 1 – Preparação (2026)</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Definição do evento âncora para o lançamento</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Avaliar opções (seminário da RBMA como referência); definir formato compatível; alinhar com a organização do evento.</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>3</v>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L561" t="b">
+        <v>1</v>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>656</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Fase 2 – Lançamento (2026)</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Averiguar sobre lançamento público no seminário RBMA</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Carol vai avaliar; preparar materiais e roteiro; realizar o lançamento no evento.</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>1</v>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L562" t="b">
+        <v>1</v>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>657</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Fase 2 – Lançamento (2026)</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Lançamento conceitual da rede</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Finalizar nota conceitual para divulgação; apresentar visão, missão, componentes e governança.</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>3</v>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L563" t="b">
+        <v>1</v>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>658</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Fase 2 – Lançamento (2026)</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Abertura de manifestação de interesse</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Disponibilizar formulário de cadastro no banco de relacionamento (sem ato formal nesta fase); divulgar o canal.</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>3</v>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L564" t="b">
+        <v>0</v>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>659</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Fase 3 – Mobilização e capacitação (2026)</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Webinars com CLEAR, parceiros e especialistas</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Definir temas e calendário; convidar palestrantes (CLEAR, parceiros internacionais, especialistas); realizar e gravar (ao menos 2).</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>3</v>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L565" t="b">
+        <v>0</v>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>660</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Fase 3 – Mobilização e capacitação (2026)</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Ciclos de estudo e debate</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Definir temas (ao menos 4) a partir das dúvidas dos participantes; curar material de consulta; conduzir rodas de debate; usar como escuta para temas formativos prioritários.</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>3</v>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L566" t="b">
+        <v>0</v>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>661</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Fase 3 – Mobilização e capacitação (2026)</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Lançamento progressivo do repositório</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Estruturar o repositório por elemento da institucionalização; carregar primeiros recursos (modelos jurídicos, planos anuais, termos de referência, casos); publicar com acesso livre.</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>3</v>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L567" t="b">
+        <v>1</v>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>662</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Fase 3 – Mobilização e capacitação (2026)</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Consolidação do banco de relacionamento</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Acompanhar e registrar manifestações de interesse; categorizar entes (referência vs. participantes); atingir meta de ~20 entes.</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>3</v>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L568" t="b">
+        <v>0</v>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>663</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Fase 3 – Mobilização e capacitação (2026)</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Validação da Teoria da Mudança</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Submeter a TdM aos parceiros e redes parceiras; incorporar ajustes; consolidar versão validada.</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>3</v>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L569" t="b">
+        <v>0</v>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>664</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Fase 3 – Mobilização e capacitação (2026)</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Fluxo de disseminação de materiais em operação</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Definir cadência e sequência; disseminar progressivamente os materiais já produzidos pelo CLEAR (cursos introdutórios, publicações, guias).</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>3</v>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L570" t="b">
+        <v>0</v>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>665</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Comunicação e articulação (transversal 2026)</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Estratégia e identidade de comunicação</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Definir públicos-alvo e mensagens-chave por público; definir tom de voz e narrativa; elaborar kit de marca básico (logo, paleta, templates de apresentação e post).</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>4</v>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L571" t="b">
+        <v>0</v>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>666</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Comunicação e articulação (transversal 2026)</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Presença digital, página online</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Conceber e publicar a página online (estrutura, textos, identidade); definir hospedagem dos materiais. [Item a resolver: onde hospedar, se no site do CLEAR ou algo por fora.]</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>4</v>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L572" t="b">
+        <v>0</v>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>667</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Comunicação e articulação (transversal 2026)</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Presença digital, LinkedIn</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Criar e configurar a página no LinkedIn; produzir conteúdos de pré-lançamento (o 'porquê' da rede) para captar interesse antes de haver lista de e-mail.</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>4</v>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L573" t="b">
+        <v>0</v>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>668</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Comunicação e articulação (transversal 2026)</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Calendário editorial e produção de conteúdo</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Definir calendário (frequência, formatos, responsáveis); produzir conteúdos de lançamento, institucionais e de divulgação de webinars e ciclos.</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>4</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L574" t="b">
+        <v>0</v>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>669</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Comunicação e articulação (transversal 2026)</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Materiais de articulação e mobilização</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Produzir material institucional (deck, one-pager, nota conceitual diagramada) e peças de convite/divulgação para webinars e ciclos.</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>4</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L575" t="b">
+        <v>0</v>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>670</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Comunicação e articulação (transversal 2026)</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Divulgação via parceiros e entes de referência</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Mobilizar as redes de contato dos parceiros e entes de referência para levar o 'porquê' e captar cadastros antes do lançamento.</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>4</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L576" t="b">
+        <v>0</v>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>671</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Comunicação e articulação (transversal 2026)</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Monitoramento de engajamento dos envios newsletter</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Acompanhar métricas básicas (alcance, participação, abertura de e-mails) e ajustar a cadência conforme os dados.</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>4</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L577" t="b">
+        <v>0</v>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>672</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Ferramentas (implementação 2026)</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Banco de relacionamento em Excel</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Montar a estrutura como tabela (uma linha por ente; campos: estágio de institucionalização, titular, contatos, atividades, follow-ups), pensada para escalar. Futuro a avaliar: Airtable, HubSpot (free) ou Attio.</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Carol; Samu; Luan; Fabrícia</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Carol, Samu, Luan, Fabrícia</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>4</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L578" t="b">
+        <v>0</v>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>673</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Ferramentas (implementação 2026)</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Escolha da ferramenta de e-mail marketing</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Comparar Brevo, MailerLite e Mailchimp (entregabilidade e custo); abrir conta.</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="n">
+        <v>0</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L579" t="b">
+        <v>0</v>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>674</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Ferramentas (implementação 2026)</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Criação de e-mail FGV</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Acionar a TI da FGV para criar e-mail da rede. Dependência com prazo, concluir antes do 1º disparo. ver autenticação</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr"/>
+      <c r="H580" t="n">
+        <v>0</v>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L580" t="b">
+        <v>0</v>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>675</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Ferramentas (implementação 2026)</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Repositório de materiais (vitrine + entrega)</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Definir vitrine (na página online) e entrega (links públicos simples que o servidor consiga abrir sem bloqueio da TI da secretaria).</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="n">
+        <v>0</v>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L581" t="b">
+        <v>1</v>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>676</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Ferramentas (implementação 2026)</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Teams como espaço de reuniões e webinars</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Usar o Teams para webinars, ciclos e reuniões, espaço de co-presença da rede em 2026.</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="n">
+        <v>0</v>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L582" t="b">
+        <v>0</v>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>677</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Régua editorial / e-mail (2026)</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Pré-lançamento - circular o 'porquê' da rede</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Antes do lançamento não há lista; circular o 'porquê' (por que a rede existe e por que fazer parte) via LinkedIn, parceiros e preparação do evento, para captar cadastros.</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="n">
+        <v>0</v>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L583" t="b">
+        <v>1</v>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>678</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Régua editorial / e-mail (2026)</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Sequência de boas-vindas (automática)</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Configurar mini-sequência automática disparada ao cadastro: (1) por que a rede existe; (2) por que entrar; (3) quem já está dentro. Pega o gestor no momento de maior interesse.</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="n">
+        <v>0</v>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L584" t="b">
+        <v>0</v>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>679</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Régua editorial / e-mail (2026)</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Régua de mobilização</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>A partir do lançamento, e-mail quinzenal fixo e ritualizado, alternando: novo material, convite a webinar/ciclo, história de um ente, destaque da comunidade.</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr"/>
+      <c r="H585" t="n">
+        <v>0</v>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L585" t="b">
+        <v>0</v>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>680</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Régua editorial / e-mail (2026)</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Pós-evento e recuperação de ausentes</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Após cada webinar/ciclo, enviar gravação + materiais a quem faltou. Regras: teto de 1 e-mail/semana; dar antes de pedir; conteúdo formativo (vedação eleitoral).</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr"/>
+      <c r="H586" t="n">
+        <v>0</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L586" t="b">
+        <v>0</v>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>681</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Abertura da adesão formal</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Finalizar modelo de carta de intenção; abordar os titulares mapeados em 2026; coletar cartas assinadas (meta: 8+ entes).</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="n">
+        <v>0</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L587" t="b">
+        <v>0</v>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>682</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Constituição do Conselho Diretor</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Definir composição (CLEAR, entes de referência, parceiros estratégicos); definir presidência rotativa e regras; instalar o Conselho.</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="n">
+        <v>0</v>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L588" t="b">
+        <v>0</v>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>683</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Instalação formal da Secretaria Executiva</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Formalizar a estrutura da Secretaria no CLEAR; definir equipe e rotinas de operação.</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="n">
+        <v>0</v>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L589" t="b">
+        <v>0</v>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>684</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Início das mentorias-piloto</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Formar pares (ente de referência + 1–2 mentorados); treinamento de nivelamento em construção de sistema de M&amp;A; planos de 9–12 meses; encontros mensais (meta: 2 mentorias no 1º sem).</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="n">
+        <v>0</v>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L590" t="b">
+        <v>0</v>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>685</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Abertura do primeiro grupo de trabalho temático</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Definir tema prioritário (a partir dos gargalos do Diagnóstico); designar coordenação (ente de referência + CLEAR); encontros e ao menos 1 produto (modelo, guia ou nota técnica).</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="n">
+        <v>0</v>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L591" t="b">
+        <v>0</v>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>686</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Webinars mensais com experiências dos entes</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Calendário mensal (ao menos 6 sessões), agora incluindo apresentações de gestores dos entes de referência; realizar e gravar.</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="n">
+        <v>0</v>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L592" t="b">
+        <v>0</v>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>687</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Primeiro encontro presencial anual</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Definir data, local e formato; organizar agenda de planejamento e deliberação coletiva; realizar no 2º semestre.</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="n">
+        <v>0</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L593" t="b">
+        <v>0</v>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>688</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Fase 4 – Primeiro ciclo operacional (2027)</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Evolução das ferramentas e do espaço de interação</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Reavaliar banco de relacionamento (Airtable/HubSpot/Attio) conforme o volume; decidir sobre plataforma de comunidade;</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="n">
+        <v>0</v>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="L594" t="b">
+        <v>0</v>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>Rede PARES 2026</t>
         </is>
       </c>
     </row>
@@ -29078,7 +31527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F797"/>
+  <dimension ref="A1:F894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49153,6 +51602,2288 @@
       </c>
       <c r="F797" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>639</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D798" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F798" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>639</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D799" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F799" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>640</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D800" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F800" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>640</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D801" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F801" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>641</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D802" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F802" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>641</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D803" s="3" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F803" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>642</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D804" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F804" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>643</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D805" s="3" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F805" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>643</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D806" s="3" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F806" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>644</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D807" s="3" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F807" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>645</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D808" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F808" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>645</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Bia S</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D809" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F809" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>646</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Bens Públicos</t>
+        </is>
+      </c>
+      <c r="D810" s="3" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F810" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>647</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="D811" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F811" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>647</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="D812" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F812" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>647</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="D813" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F813" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>647</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="D814" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F814" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>648</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F815" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>648</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F816" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>648</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F817" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>649</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F818" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>649</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F819" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>649</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F820" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>650</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F821" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>650</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F822" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>650</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F823" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>651</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Lycia</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F824" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>652</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F825" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>652</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F826" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>652</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F827" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>652</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F828" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>653</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F829" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>653</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F830" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>653</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F831" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>654</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F832" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>654</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F833" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>654</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="F834" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>655</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F835" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>655</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F836" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>655</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F837" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>656</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F838" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>657</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F839" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>657</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F840" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>657</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F841" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>658</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F842" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>658</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F843" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>658</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F844" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>659</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F845" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>659</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F846" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>659</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F847" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>660</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F848" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>660</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F849" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>660</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F850" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>661</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F851" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>661</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F852" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>661</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F853" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>662</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F854" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>662</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F855" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>662</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F856" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>663</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F857" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>663</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F858" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>663</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F859" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>664</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F860" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>664</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F861" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>664</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F862" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>665</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F863" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>665</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F864" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>665</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F865" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>665</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F866" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>666</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F867" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>666</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F868" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>666</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F869" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>666</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F870" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>667</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F871" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>667</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F872" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>667</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F873" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>667</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F874" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>668</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F875" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>668</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F876" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>668</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F877" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>668</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F878" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>669</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F879" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>669</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F880" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>669</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F881" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>669</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F882" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>670</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F883" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>670</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F884" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>670</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F885" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>670</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F886" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>671</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F887" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>671</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F888" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>671</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F889" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>671</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F890" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>672</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F891" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>672</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Samu</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F892" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>672</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F893" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>672</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Fabrícia</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Não Iniciado</t>
+        </is>
+      </c>
+      <c r="F894" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -54124,7 +58855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54201,6 +58932,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>TCE ES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rede PARES</t>
         </is>
       </c>
     </row>

--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -30852,8 +30852,6 @@
           <t>Comparar Brevo, MailerLite e Mailchimp (entregabilidade e custo); abrir conta.</t>
         </is>
       </c>
-      <c r="F579" t="inlineStr"/>
-      <c r="G579" t="inlineStr"/>
       <c r="H579" t="n">
         <v>0</v>
       </c>
@@ -30895,8 +30893,6 @@
           <t>Acionar a TI da FGV para criar e-mail da rede. Dependência com prazo, concluir antes do 1º disparo. ver autenticação</t>
         </is>
       </c>
-      <c r="F580" t="inlineStr"/>
-      <c r="G580" t="inlineStr"/>
       <c r="H580" t="n">
         <v>0</v>
       </c>
@@ -30938,8 +30934,6 @@
           <t>Definir vitrine (na página online) e entrega (links públicos simples que o servidor consiga abrir sem bloqueio da TI da secretaria).</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
       <c r="H581" t="n">
         <v>0</v>
       </c>
@@ -30981,8 +30975,6 @@
           <t>Usar o Teams para webinars, ciclos e reuniões, espaço de co-presença da rede em 2026.</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr"/>
-      <c r="G582" t="inlineStr"/>
       <c r="H582" t="n">
         <v>0</v>
       </c>
@@ -31024,8 +31016,6 @@
           <t>Antes do lançamento não há lista; circular o 'porquê' (por que a rede existe e por que fazer parte) via LinkedIn, parceiros e preparação do evento, para captar cadastros.</t>
         </is>
       </c>
-      <c r="F583" t="inlineStr"/>
-      <c r="G583" t="inlineStr"/>
       <c r="H583" t="n">
         <v>0</v>
       </c>
@@ -31067,8 +31057,6 @@
           <t>Configurar mini-sequência automática disparada ao cadastro: (1) por que a rede existe; (2) por que entrar; (3) quem já está dentro. Pega o gestor no momento de maior interesse.</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr"/>
-      <c r="G584" t="inlineStr"/>
       <c r="H584" t="n">
         <v>0</v>
       </c>
@@ -31110,8 +31098,6 @@
           <t>A partir do lançamento, e-mail quinzenal fixo e ritualizado, alternando: novo material, convite a webinar/ciclo, história de um ente, destaque da comunidade.</t>
         </is>
       </c>
-      <c r="F585" t="inlineStr"/>
-      <c r="G585" t="inlineStr"/>
       <c r="H585" t="n">
         <v>0</v>
       </c>
@@ -31153,8 +31139,6 @@
           <t>Após cada webinar/ciclo, enviar gravação + materiais a quem faltou. Regras: teto de 1 e-mail/semana; dar antes de pedir; conteúdo formativo (vedação eleitoral).</t>
         </is>
       </c>
-      <c r="F586" t="inlineStr"/>
-      <c r="G586" t="inlineStr"/>
       <c r="H586" t="n">
         <v>0</v>
       </c>
@@ -31196,8 +31180,6 @@
           <t>Finalizar modelo de carta de intenção; abordar os titulares mapeados em 2026; coletar cartas assinadas (meta: 8+ entes).</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr"/>
-      <c r="G587" t="inlineStr"/>
       <c r="H587" t="n">
         <v>0</v>
       </c>
@@ -31239,8 +31221,6 @@
           <t>Definir composição (CLEAR, entes de referência, parceiros estratégicos); definir presidência rotativa e regras; instalar o Conselho.</t>
         </is>
       </c>
-      <c r="F588" t="inlineStr"/>
-      <c r="G588" t="inlineStr"/>
       <c r="H588" t="n">
         <v>0</v>
       </c>
@@ -31282,8 +31262,6 @@
           <t>Formalizar a estrutura da Secretaria no CLEAR; definir equipe e rotinas de operação.</t>
         </is>
       </c>
-      <c r="F589" t="inlineStr"/>
-      <c r="G589" t="inlineStr"/>
       <c r="H589" t="n">
         <v>0</v>
       </c>
@@ -31325,8 +31303,6 @@
           <t>Formar pares (ente de referência + 1–2 mentorados); treinamento de nivelamento em construção de sistema de M&amp;A; planos de 9–12 meses; encontros mensais (meta: 2 mentorias no 1º sem).</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr"/>
-      <c r="G590" t="inlineStr"/>
       <c r="H590" t="n">
         <v>0</v>
       </c>
@@ -31368,8 +31344,6 @@
           <t>Definir tema prioritário (a partir dos gargalos do Diagnóstico); designar coordenação (ente de referência + CLEAR); encontros e ao menos 1 produto (modelo, guia ou nota técnica).</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr"/>
-      <c r="G591" t="inlineStr"/>
       <c r="H591" t="n">
         <v>0</v>
       </c>
@@ -31411,8 +31385,6 @@
           <t>Calendário mensal (ao menos 6 sessões), agora incluindo apresentações de gestores dos entes de referência; realizar e gravar.</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr"/>
-      <c r="G592" t="inlineStr"/>
       <c r="H592" t="n">
         <v>0</v>
       </c>
@@ -31454,8 +31426,6 @@
           <t>Definir data, local e formato; organizar agenda de planejamento e deliberação coletiva; realizar no 2º semestre.</t>
         </is>
       </c>
-      <c r="F593" t="inlineStr"/>
-      <c r="G593" t="inlineStr"/>
       <c r="H593" t="n">
         <v>0</v>
       </c>
@@ -31497,8 +31467,6 @@
           <t>Reavaliar banco de relacionamento (Airtable/HubSpot/Attio) conforme o volume; decidir sobre plataforma de comunidade;</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr"/>
-      <c r="G594" t="inlineStr"/>
       <c r="H594" t="n">
         <v>0</v>
       </c>
@@ -58953,7 +58921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D386"/>
+  <dimension ref="A1:D297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58981,12 +58949,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -59001,12 +58969,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -59021,12 +58989,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -59041,12 +59009,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -59061,12 +59029,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -59081,16 +59049,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -59101,16 +59069,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -59121,16 +59089,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -59141,176 +59109,176 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - CURSO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -59321,16 +59289,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -59341,16 +59309,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -59361,16 +59329,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -59381,176 +59349,176 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -59561,16 +59529,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -59581,56 +59549,56 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -59641,16 +59609,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -59661,16 +59629,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -59681,16 +59649,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -59701,16 +59669,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -59721,16 +59689,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -59741,40 +59709,40 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -59786,11 +59754,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -59806,11 +59774,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -59826,11 +59794,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>TCE - ASSESSORIA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -59841,16 +59809,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -59861,16 +59829,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -59881,16 +59849,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -59901,16 +59869,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -59921,16 +59889,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -59941,16 +59909,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -59961,16 +59929,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -59981,16 +59949,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - OFICINA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -60001,16 +59969,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -60021,16 +59989,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -60041,16 +60009,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -60061,16 +60029,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -60081,16 +60049,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PRIME - FUNDAMENTOS</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -60101,16 +60069,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -60121,16 +60089,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -60141,16 +60109,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -60161,16 +60129,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -60181,16 +60149,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -60201,16 +60169,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -60221,16 +60189,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -60241,16 +60209,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -60261,16 +60229,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -60281,12 +60249,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -60294,19 +60262,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -60314,19 +60282,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -60334,19 +60302,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -60354,19 +60322,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -60374,19 +60342,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -60394,19 +60362,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -60414,147 +60382,147 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - AV EXECUTIVA</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -60566,11 +60534,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ARTIGO SISTEMA</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -60581,16 +60549,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ARTIGO SISTEMA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -60601,16 +60569,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ARTIGO SISTEMA</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -60621,16 +60589,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ARTIGO SISTEMA</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -60641,16 +60609,16 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ARTIGO SISTEMA</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -60661,16 +60629,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ARTIGO SISTEMA</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -60681,16 +60649,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -60701,16 +60669,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -60721,16 +60689,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PRIME - HANDS ON</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -60741,16 +60709,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -60761,16 +60729,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -60781,16 +60749,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -60801,12 +60769,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -60821,12 +60789,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -60841,12 +60809,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -60861,76 +60829,76 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - ASSESSORIA TÉCNICA</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -60941,16 +60909,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -60961,16 +60929,16 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -60981,16 +60949,16 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -61001,56 +60969,56 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -61061,16 +61029,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -61081,16 +61049,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -61101,16 +61069,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>IU - CURSO AUTOINSTRUCIONAL</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -61121,12 +61089,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -61141,12 +61109,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -61161,12 +61129,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -61181,12 +61149,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -61201,12 +61169,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -61221,16 +61189,16 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -61241,16 +61209,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -61266,11 +61234,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -61286,11 +61254,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -61306,11 +61274,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -61326,11 +61294,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -61346,11 +61314,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -61361,116 +61329,116 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PRIME - AV IMPACTO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -61481,16 +61449,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -61501,16 +61469,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -61521,16 +61489,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -61541,16 +61509,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Fred</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>FINEP</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -61566,7 +61534,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -61586,7 +61554,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -61606,7 +61574,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -61621,16 +61589,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -61641,16 +61609,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -61661,16 +61629,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -61681,16 +61649,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -61701,16 +61669,16 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -61721,16 +61689,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -61746,11 +61714,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -61766,11 +61734,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -61786,11 +61754,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -61801,16 +61769,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -61821,16 +61789,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -61841,16 +61809,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Fabrícia</t>
+          <t>Hisrael</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PRIME - OFICINAS INOVAÇÃO</t>
+          <t>SERGIPE GUIAS</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -61866,11 +61834,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -61886,11 +61854,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -61901,16 +61869,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -61921,16 +61889,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -61941,16 +61909,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -61961,16 +61929,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE CURSO</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -61981,16 +61949,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -62001,16 +61969,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -62021,16 +61989,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -62041,16 +62009,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EVALAC</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -62061,16 +62029,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -62081,16 +62049,16 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -62101,16 +62069,16 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -62121,16 +62089,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -62141,16 +62109,16 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>SERGIPE ASSESSORIA</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -62161,320 +62129,320 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -62486,15 +62454,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -62506,15 +62474,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -62526,127 +62494,127 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>REDECA</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -62654,163 +62622,163 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>FUNDRAISING</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -62821,16 +62789,16 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -62841,16 +62809,16 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TCE - CURSO</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -62861,12 +62829,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -62881,16 +62849,16 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -62901,16 +62869,16 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>GLOCAL</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -62921,16 +62889,16 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bia B</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>PROCESSO SELETIVO</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -62941,12 +62909,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>PROCESSO SELETIVO</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -62954,23 +62922,23 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -62981,16 +62949,16 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -63001,16 +62969,16 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -63021,16 +62989,16 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -63041,16 +63009,16 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -63061,16 +63029,16 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -63081,16 +63049,16 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -63101,56 +63069,56 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -63161,16 +63129,16 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -63181,16 +63149,16 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -63201,16 +63169,16 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Luigi</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>SICREDI</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -63221,16 +63189,16 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -63241,16 +63209,16 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -63261,16 +63229,16 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -63281,16 +63249,16 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Luan</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -63301,20 +63269,20 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -63326,15 +63294,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -63346,15 +63314,15 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -63366,15 +63334,15 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -63386,127 +63354,127 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TCE - ASSESSORIA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>EVALAC</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>REDECA</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>REDECA</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>REDECA</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>REDECA</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -63514,39 +63482,39 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>IU - OFICINA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -63554,159 +63522,159 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -63721,12 +63689,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>BENS PÚBLICOS</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -63734,119 +63702,119 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -63854,19 +63822,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -63874,19 +63842,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -63894,19 +63862,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -63914,19 +63882,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -63934,19 +63902,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -63954,19 +63922,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia B</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -63974,19 +63942,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Lycia</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -64001,12 +63969,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Lycia</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -64021,216 +63989,216 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Fred</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IU - AV EXECUTIVA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>IU - ARTIGO SISTEMA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Caio</t>
+          <t>Samu</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>IU - ARTIGO SISTEMA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IU - ARTIGO SISTEMA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IU - ARTIGO SISTEMA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>IU - ARTIGO SISTEMA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Bia S</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>IU - ARTIGO SISTEMA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -64241,16 +64209,16 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -64261,16 +64229,16 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -64281,16 +64249,16 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -64301,16 +64269,16 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -64321,16 +64289,16 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -64341,16 +64309,16 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -64361,56 +64329,56 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -64421,72 +64389,72 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Hisrael</t>
+          <t>Caio</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>IU - ASSESSORIA TÉCNICA</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -64494,19 +64462,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Bia S</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -64514,279 +64482,279 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Samu</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>IU - CURSO AUTOINSTRUCIONAL</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -64794,19 +64762,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Fabrícia</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -64814,23 +64782,23 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -64841,16 +64809,16 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -64861,1818 +64829,38 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Luan</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>FINEP</t>
+          <t>PRIME</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D297" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>12</v>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>8</v>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>9</v>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>10</v>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>11</v>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>12</v>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>Fred</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>8</v>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Fred</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>9</v>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Fred</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>10</v>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Fred</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>11</v>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Fred</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>FINEP</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>12</v>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Bia S</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>6</v>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Bia S</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>7</v>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Bia S</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>8</v>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>6</v>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>7</v>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>8</v>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Cecilia</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>6</v>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Cecilia</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>7</v>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Cecilia</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>8</v>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>6</v>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>7</v>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>8</v>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Hisrael</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>6</v>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Hisrael</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>7</v>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Hisrael</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>SERGIPE GUIAS</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>8</v>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>SERGIPE CURSO</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>8</v>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>SERGIPE CURSO</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>9</v>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>SERGIPE CURSO</t>
-        </is>
-      </c>
-      <c r="C326" t="n">
-        <v>8</v>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>SERGIPE CURSO</t>
-        </is>
-      </c>
-      <c r="C327" t="n">
-        <v>9</v>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Luan</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>SERGIPE CURSO</t>
-        </is>
-      </c>
-      <c r="C328" t="n">
-        <v>8</v>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Luan</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>SERGIPE CURSO</t>
-        </is>
-      </c>
-      <c r="C329" t="n">
-        <v>9</v>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C330" t="n">
-        <v>10</v>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C331" t="n">
-        <v>11</v>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C332" t="n">
-        <v>12</v>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C333" t="n">
-        <v>10</v>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C334" t="n">
-        <v>11</v>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
-        <v>12</v>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Cecilia</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C336" t="n">
-        <v>10</v>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Cecilia</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C337" t="n">
-        <v>11</v>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Cecilia</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>SERGIPE ASSESSORIA</t>
-        </is>
-      </c>
-      <c r="C338" t="n">
-        <v>12</v>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C339" t="n">
-        <v>5</v>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C340" t="n">
-        <v>6</v>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C341" t="n">
-        <v>7</v>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C342" t="n">
-        <v>8</v>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>9</v>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>10</v>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C345" t="n">
-        <v>11</v>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="C346" t="n">
-        <v>12</v>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C347" t="n">
-        <v>5</v>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>6</v>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>7</v>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>8</v>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>9</v>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>10</v>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>11</v>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>BENS PÚBLICOS</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>12</v>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>5</v>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>6</v>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>7</v>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>8</v>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>9</v>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>10</v>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>11</v>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Bia B</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C362" t="n">
-        <v>12</v>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C363" t="n">
-        <v>5</v>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C364" t="n">
-        <v>6</v>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>7</v>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>8</v>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>9</v>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C368" t="n">
-        <v>10</v>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C369" t="n">
-        <v>11</v>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C370" t="n">
-        <v>12</v>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C371" t="n">
-        <v>5</v>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C372" t="n">
-        <v>6</v>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C373" t="n">
-        <v>7</v>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C374" t="n">
-        <v>8</v>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C375" t="n">
-        <v>9</v>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C376" t="n">
-        <v>10</v>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C377" t="n">
-        <v>11</v>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Samu</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>FUNDRAISING</t>
-        </is>
-      </c>
-      <c r="C378" t="n">
-        <v>12</v>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C379" t="n">
-        <v>5</v>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C380" t="n">
-        <v>6</v>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C381" t="n">
-        <v>5</v>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Fabrícia</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C382" t="n">
-        <v>6</v>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C383" t="n">
-        <v>5</v>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>GLOCAL</t>
-        </is>
-      </c>
-      <c r="C384" t="n">
-        <v>6</v>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>PROCESSO SELETIVO</t>
-        </is>
-      </c>
-      <c r="C385" t="n">
-        <v>5</v>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>PROCESSO SELETIVO</t>
-        </is>
-      </c>
-      <c r="C386" t="n">
-        <v>5</v>
-      </c>
-      <c r="D386" t="inlineStr">
         <is>
           <t>B</t>
         </is>

--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -440,7 +440,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Última atualização: 2026-07-09</t>
+          <t>Última atualização: 2026-07-13</t>
         </is>
       </c>
     </row>
@@ -27466,7 +27466,7 @@
         <v>1</v>
       </c>
       <c r="I484" s="3" t="n">
-        <v>46212</v>
+        <v>46240</v>
       </c>
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
@@ -27523,7 +27523,7 @@
         <v>1</v>
       </c>
       <c r="I485" s="3" t="n">
-        <v>46212</v>
+        <v>46240</v>
       </c>
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
@@ -27580,7 +27580,7 @@
         <v>2</v>
       </c>
       <c r="I486" s="3" t="n">
-        <v>46219</v>
+        <v>46247</v>
       </c>
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
@@ -27637,7 +27637,7 @@
         <v>1</v>
       </c>
       <c r="I487" s="3" t="n">
-        <v>46225</v>
+        <v>46247</v>
       </c>
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
@@ -27694,7 +27694,7 @@
         <v>1</v>
       </c>
       <c r="I488" s="3" t="n">
-        <v>46227</v>
+        <v>46254</v>
       </c>
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
@@ -27751,7 +27751,7 @@
         <v>2</v>
       </c>
       <c r="I489" s="3" t="n">
-        <v>46232</v>
+        <v>46259</v>
       </c>
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
@@ -27808,7 +27808,7 @@
         <v>2</v>
       </c>
       <c r="I490" s="3" t="n">
-        <v>46233</v>
+        <v>46261</v>
       </c>
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
@@ -27865,7 +27865,7 @@
         <v>2</v>
       </c>
       <c r="I491" s="3" t="n">
-        <v>46245</v>
+        <v>46268</v>
       </c>
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
@@ -27922,7 +27922,7 @@
         <v>1</v>
       </c>
       <c r="I492" s="3" t="n">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
@@ -27979,7 +27979,7 @@
         <v>1</v>
       </c>
       <c r="I493" s="3" t="n">
-        <v>46252</v>
+        <v>46275</v>
       </c>
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr">
@@ -28036,7 +28036,7 @@
         <v>1</v>
       </c>
       <c r="I494" s="3" t="n">
-        <v>46255</v>
+        <v>46280</v>
       </c>
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
@@ -28093,7 +28093,7 @@
         <v>3</v>
       </c>
       <c r="I495" s="3" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
@@ -28150,7 +28150,7 @@
         <v>1</v>
       </c>
       <c r="I496" s="3" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
@@ -28207,7 +28207,7 @@
         <v>1</v>
       </c>
       <c r="I497" s="3" t="n">
-        <v>46283</v>
+        <v>46294</v>
       </c>
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
@@ -28264,7 +28264,7 @@
         <v>1</v>
       </c>
       <c r="I498" s="3" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
@@ -28321,7 +28321,7 @@
         <v>2</v>
       </c>
       <c r="I499" s="3" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
@@ -28378,7 +28378,7 @@
         <v>1</v>
       </c>
       <c r="I500" s="3" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
@@ -54983,7 +54983,7 @@
         </is>
       </c>
       <c r="D709" s="3" t="n">
-        <v>46212</v>
+        <v>46240</v>
       </c>
       <c r="E709" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         </is>
       </c>
       <c r="D710" s="3" t="n">
-        <v>46212</v>
+        <v>46240</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         </is>
       </c>
       <c r="D711" s="3" t="n">
-        <v>46219</v>
+        <v>46247</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
@@ -55061,7 +55061,7 @@
         </is>
       </c>
       <c r="D712" s="3" t="n">
-        <v>46219</v>
+        <v>46247</v>
       </c>
       <c r="E712" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         </is>
       </c>
       <c r="D713" s="3" t="n">
-        <v>46225</v>
+        <v>46247</v>
       </c>
       <c r="E713" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         </is>
       </c>
       <c r="D714" s="3" t="n">
-        <v>46227</v>
+        <v>46254</v>
       </c>
       <c r="E714" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         </is>
       </c>
       <c r="D715" s="3" t="n">
-        <v>46232</v>
+        <v>46259</v>
       </c>
       <c r="E715" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         </is>
       </c>
       <c r="D716" s="3" t="n">
-        <v>46232</v>
+        <v>46259</v>
       </c>
       <c r="E716" t="inlineStr">
         <is>
@@ -55191,7 +55191,7 @@
         </is>
       </c>
       <c r="D717" s="3" t="n">
-        <v>46233</v>
+        <v>46261</v>
       </c>
       <c r="E717" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         </is>
       </c>
       <c r="D718" s="3" t="n">
-        <v>46233</v>
+        <v>46261</v>
       </c>
       <c r="E718" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         </is>
       </c>
       <c r="D719" s="3" t="n">
-        <v>46245</v>
+        <v>46268</v>
       </c>
       <c r="E719" t="inlineStr">
         <is>
@@ -55269,7 +55269,7 @@
         </is>
       </c>
       <c r="D720" s="3" t="n">
-        <v>46245</v>
+        <v>46268</v>
       </c>
       <c r="E720" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         </is>
       </c>
       <c r="D721" s="3" t="n">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="E721" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         </is>
       </c>
       <c r="D722" s="3" t="n">
-        <v>46252</v>
+        <v>46275</v>
       </c>
       <c r="E722" t="inlineStr">
         <is>
@@ -55347,7 +55347,7 @@
         </is>
       </c>
       <c r="D723" s="3" t="n">
-        <v>46255</v>
+        <v>46280</v>
       </c>
       <c r="E723" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         </is>
       </c>
       <c r="D724" s="3" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="E724" t="inlineStr">
         <is>
@@ -55399,7 +55399,7 @@
         </is>
       </c>
       <c r="D725" s="3" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="E725" t="inlineStr">
         <is>
@@ -55425,7 +55425,7 @@
         </is>
       </c>
       <c r="D726" s="3" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="E726" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         </is>
       </c>
       <c r="D727" s="3" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="E727" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         </is>
       </c>
       <c r="D728" s="3" t="n">
-        <v>46283</v>
+        <v>46294</v>
       </c>
       <c r="E728" t="inlineStr">
         <is>
@@ -55503,7 +55503,7 @@
         </is>
       </c>
       <c r="D729" s="3" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="E729" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         </is>
       </c>
       <c r="D730" s="3" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="E730" t="inlineStr">
         <is>
@@ -55555,7 +55555,7 @@
         </is>
       </c>
       <c r="D731" s="3" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="E731" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         </is>
       </c>
       <c r="D732" s="3" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="E732" t="inlineStr">
         <is>
